--- a/analytikI/vystup.xlsx
+++ b/analytikI/vystup.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NovyHark" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Osoby" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Firmy" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,6 +29,10 @@
     <font>
       <b val="1"/>
       <color rgb="0000FF00"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000000FF"/>
     </font>
   </fonts>
   <fills count="2">
@@ -51,9 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -428,7 +433,7 @@
           <t>Meno</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Vek</t>
         </is>
@@ -443,6 +448,10 @@
       <c r="B2" t="n">
         <v>30</v>
       </c>
+      <c r="C2">
+        <f>SUM(B2:B3)</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -452,12 +461,6 @@
       </c>
       <c r="B3" t="n">
         <v>25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4">
-        <f>SUM(B2:B3)</f>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -473,15 +476,7 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Dáta</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>